--- a/data/trans_dic/IP08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 14,4</t>
+          <t>5,64; 14,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 19,56</t>
+          <t>10,31; 19,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 12,11</t>
+          <t>4,11; 11,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 23,08</t>
+          <t>8,09; 22,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 18,21</t>
+          <t>8,36; 17,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 22,36</t>
+          <t>12,7; 22,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 15,21</t>
+          <t>6,58; 15,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,73; 27,24</t>
+          <t>12,05; 29,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,44</t>
+          <t>8,21; 15,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 19,33</t>
+          <t>12,45; 19,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,88</t>
+          <t>6,31; 11,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 22,18</t>
+          <t>11,91; 22,14</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 13,1</t>
+          <t>7,03; 12,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,66</t>
+          <t>8,98; 15,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 12,4</t>
+          <t>6,25; 12,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,33</t>
+          <t>3,48; 9,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,48; 17,37</t>
+          <t>10,28; 17,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 17,94</t>
+          <t>10,71; 17,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,21</t>
+          <t>5,53; 11,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 17,2</t>
+          <t>8,89; 16,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,16</t>
+          <t>9,76; 14,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 15,77</t>
+          <t>10,7; 15,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 10,74</t>
+          <t>6,56; 10,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,15</t>
+          <t>6,87; 12,11</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 16,07</t>
+          <t>7,11; 16,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 17,96</t>
+          <t>9,17; 17,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,8</t>
+          <t>2,68; 8,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 14,42</t>
+          <t>6,2; 14,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 15,65</t>
+          <t>6,87; 15,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 13,99</t>
+          <t>6,12; 13,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,79</t>
+          <t>1,24; 5,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 16,17</t>
+          <t>7,39; 15,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,7; 14,15</t>
+          <t>7,85; 13,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 14,02</t>
+          <t>8,46; 14,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,22</t>
+          <t>2,47; 5,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,7; 13,45</t>
+          <t>7,92; 13,41</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,15</t>
+          <t>2,08; 6,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,59</t>
+          <t>5,02; 11,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,71</t>
+          <t>3,44; 9,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 17,74</t>
+          <t>6,96; 17,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 12,22</t>
+          <t>5,84; 12,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 18,02</t>
+          <t>9,17; 17,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,84</t>
+          <t>4,14; 10,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,1; 25,12</t>
+          <t>8,9; 23,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,6</t>
+          <t>4,68; 8,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 13,67</t>
+          <t>8,12; 13,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,95</t>
+          <t>4,57; 9,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 19,11</t>
+          <t>9,04; 18,66</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,17</t>
+          <t>6,51; 10,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 13,54</t>
+          <t>9,95; 13,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,49</t>
+          <t>5,29; 8,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,45</t>
+          <t>7,47; 12,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,54</t>
+          <t>9,66; 13,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,64</t>
+          <t>11,64; 15,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,51</t>
+          <t>5,56; 8,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,49; 17,19</t>
+          <t>10,61; 17,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,32</t>
+          <t>8,77; 11,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,32; 14,19</t>
+          <t>11,25; 14,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,07</t>
+          <t>5,73; 7,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,07</t>
+          <t>9,69; 14,64</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21008</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9682</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8173</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15530</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24939</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>25535</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45947</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22313</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>19622</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5992; 15489</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15050; 27973</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5394; 15201</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4654; 12908</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10147; 21778</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>18534; 32766</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8166; 18670</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7403; 18021</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>18683; 34259</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36350; 56823</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16112; 30466</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>14167; 26340</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>24665</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28288</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18516</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9292</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>22659</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>59806</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>66709</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39585</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>31950</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>17808; 32750</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21215; 37203</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13102; 25689</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5541; 14834</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26079; 43859</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>28808; 48278</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14099; 28960</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>16226; 30485</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>49457; 72375</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>54048; 80166</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>30497; 50060</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>23475; 41383</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>13699</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20199</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8903</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>23429</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>28737</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>35160</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14834</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>40167</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9063; 20569</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14395; 27428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5055; 15162</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10733; 24339</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9679; 21741</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9702; 21560</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2340; 10636</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>15694; 32452</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>21079; 37473</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>26690; 44724</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9307; 22054</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>30519; 51705</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7874</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13375</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10545</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29346</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24098</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>41492</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>25643</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37473</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22361</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>70838</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4033; 12823</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8603; 19736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5931; 16679</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>19130; 48130</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12039; 25535</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16503; 31526</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7203; 18480</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>27015; 72497</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>18716; 33965</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>28513; 48151</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>15836; 31279</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>52292; 107939</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>56243</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>82869</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47647</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>63548</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>99029</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>139721</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>185289</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>99093</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>162578</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>44360; 69145</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70716; 97881</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>37149; 58633</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>49681; 83860</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>69713; 97968</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>87689; 118812</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>41248; 63708</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>80646; 131983</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>123077; 160145</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>164766; 207436</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>82772; 114153</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>138048; 208543</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 14,59</t>
+          <t>5,76; 15,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 19,16</t>
+          <t>10,26; 20,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,59</t>
+          <t>4,46; 11,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,09; 22,44</t>
+          <t>8,13; 21,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,94</t>
+          <t>8,83; 18,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,7; 22,44</t>
+          <t>12,68; 23,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 15,04</t>
+          <t>6,57; 15,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,05; 29,33</t>
+          <t>11,08; 27,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 15,06</t>
+          <t>8,29; 15,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 19,46</t>
+          <t>12,76; 19,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 11,93</t>
+          <t>6,14; 11,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,91; 22,14</t>
+          <t>12,07; 22,12</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,93</t>
+          <t>7,1; 12,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 15,75</t>
+          <t>8,55; 15,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,26</t>
+          <t>6,0; 11,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,31</t>
+          <t>3,65; 9,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 17,28</t>
+          <t>10,47; 17,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,71; 17,95</t>
+          <t>11,38; 18,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,36</t>
+          <t>5,79; 11,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 16,7</t>
+          <t>8,33; 16,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 14,28</t>
+          <t>9,61; 14,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,7; 15,87</t>
+          <t>10,93; 15,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,77</t>
+          <t>6,62; 10,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,11</t>
+          <t>7,02; 11,97</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,13</t>
+          <t>7,13; 16,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,46</t>
+          <t>8,68; 17,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,03</t>
+          <t>2,61; 8,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 14,06</t>
+          <t>6,22; 14,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 15,44</t>
+          <t>6,88; 16,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 13,6</t>
+          <t>6,04; 14,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,64</t>
+          <t>1,22; 5,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 15,27</t>
+          <t>7,29; 16,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,96</t>
+          <t>8,08; 14,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 14,17</t>
+          <t>8,28; 14,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,84</t>
+          <t>2,47; 5,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 13,41</t>
+          <t>7,69; 13,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,61</t>
+          <t>2,18; 6,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,52</t>
+          <t>4,95; 11,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,67</t>
+          <t>3,45; 10,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 17,5</t>
+          <t>6,74; 17,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,39</t>
+          <t>5,77; 12,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,52</t>
+          <t>9,61; 18,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 10,62</t>
+          <t>3,81; 10,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,9; 23,89</t>
+          <t>8,98; 25,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,49</t>
+          <t>4,6; 8,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 13,71</t>
+          <t>8,2; 13,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,03</t>
+          <t>4,52; 9,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 18,66</t>
+          <t>8,97; 18,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,15</t>
+          <t>6,68; 10,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,77</t>
+          <t>9,79; 13,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,35</t>
+          <t>5,3; 8,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,61</t>
+          <t>7,39; 12,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 13,57</t>
+          <t>9,63; 13,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,77</t>
+          <t>11,61; 15,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,59</t>
+          <t>5,45; 8,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,37</t>
+          <t>10,59; 17,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,41</t>
+          <t>8,62; 11,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,17</t>
+          <t>11,23; 14,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,91</t>
+          <t>5,76; 8,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,64</t>
+          <t>9,66; 14,09</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5992; 15489</t>
+          <t>6113; 15984</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15050; 27973</t>
+          <t>14983; 29238</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5394; 15201</t>
+          <t>5853; 14962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4654; 12908</t>
+          <t>4673; 12423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10147; 21778</t>
+          <t>10712; 22454</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18534; 32766</t>
+          <t>18507; 33630</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8166; 18670</t>
+          <t>8153; 18783</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7403; 18021</t>
+          <t>6807; 16677</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18683; 34259</t>
+          <t>18853; 34273</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36350; 56823</t>
+          <t>37249; 56912</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16112; 30466</t>
+          <t>15676; 30372</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14167; 26340</t>
+          <t>14362; 26313</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17808; 32750</t>
+          <t>17972; 32826</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21215; 37203</t>
+          <t>20191; 36197</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13102; 25689</t>
+          <t>12574; 25096</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5541; 14834</t>
+          <t>5822; 15270</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26079; 43859</t>
+          <t>26562; 44309</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28808; 48278</t>
+          <t>30614; 50071</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14099; 28960</t>
+          <t>14773; 29069</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16226; 30485</t>
+          <t>15205; 30644</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49457; 72375</t>
+          <t>48698; 71909</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54048; 80166</t>
+          <t>55199; 80129</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30497; 50060</t>
+          <t>30762; 50274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23475; 41383</t>
+          <t>24001; 40925</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9063; 20569</t>
+          <t>9090; 21371</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14395; 27428</t>
+          <t>13639; 27423</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5055; 15162</t>
+          <t>4935; 15427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10733; 24339</t>
+          <t>10770; 24872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9679; 21741</t>
+          <t>9683; 22717</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9702; 21560</t>
+          <t>9583; 22429</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2340; 10636</t>
+          <t>2293; 10563</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15694; 32452</t>
+          <t>15497; 34091</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21079; 37473</t>
+          <t>21680; 38122</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26690; 44724</t>
+          <t>26147; 44501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9307; 22054</t>
+          <t>9336; 22000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30519; 51705</t>
+          <t>29662; 51539</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4033; 12823</t>
+          <t>4226; 13475</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8603; 19736</t>
+          <t>8482; 20317</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5931; 16679</t>
+          <t>5949; 18095</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19130; 48130</t>
+          <t>18549; 48746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12039; 25535</t>
+          <t>11897; 25453</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16503; 31526</t>
+          <t>17297; 32616</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7203; 18480</t>
+          <t>6624; 17635</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27015; 72497</t>
+          <t>27264; 78653</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18716; 33965</t>
+          <t>18420; 34620</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28513; 48151</t>
+          <t>28823; 47173</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15836; 31279</t>
+          <t>15680; 32061</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52292; 107939</t>
+          <t>51887; 106618</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44360; 69145</t>
+          <t>45465; 68573</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70716; 97881</t>
+          <t>69593; 97242</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37149; 58633</t>
+          <t>37234; 59554</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49681; 83860</t>
+          <t>49148; 82883</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>69713; 97968</t>
+          <t>69555; 98523</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87689; 118812</t>
+          <t>87486; 116351</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41248; 63708</t>
+          <t>40454; 62554</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80646; 131983</t>
+          <t>80504; 133640</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>123077; 160145</t>
+          <t>120983; 159801</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164766; 207436</t>
+          <t>164447; 205744</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82772; 114153</t>
+          <t>83244; 115865</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>138048; 208543</t>
+          <t>137584; 200782</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,79%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18,6%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,42%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 15,06</t>
+          <t>8,67; 18,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 20,02</t>
+          <t>12,33; 22,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 11,41</t>
+          <t>6,43; 15,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 21,6</t>
+          <t>11,94; 27,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 18,5</t>
+          <t>5,32; 14,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,68; 23,04</t>
+          <t>10,13; 19,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,13</t>
+          <t>4,29; 12,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 27,14</t>
+          <t>8,32; 24,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 15,06</t>
+          <t>8,15; 15,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 19,49</t>
+          <t>12,75; 19,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 11,89</t>
+          <t>6,25; 11,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 22,12</t>
+          <t>11,5; 22,61</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,74%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,97%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>8,83%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,96</t>
+          <t>10,48; 17,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,55; 15,32</t>
+          <t>11,02; 17,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,97</t>
+          <t>5,65; 11,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,59</t>
+          <t>8,47; 16,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 17,46</t>
+          <t>7,11; 13,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 18,61</t>
+          <t>8,87; 15,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,4</t>
+          <t>6,17; 12,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 16,79</t>
+          <t>3,8; 9,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 14,18</t>
+          <t>9,51; 14,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,93; 15,86</t>
+          <t>10,89; 15,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,82</t>
+          <t>6,61; 10,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,97</t>
+          <t>6,99; 12,03</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10,74%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,86%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 16,76</t>
+          <t>6,82; 15,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 17,46</t>
+          <t>6,25; 13,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,17</t>
+          <t>1,46; 5,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 14,37</t>
+          <t>7,18; 15,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,13</t>
+          <t>6,74; 16,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 14,14</t>
+          <t>8,71; 17,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,6</t>
+          <t>2,59; 7,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 16,04</t>
+          <t>6,43; 14,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 14,21</t>
+          <t>7,7; 14,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,1</t>
+          <t>8,47; 14,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,83</t>
+          <t>2,54; 6,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 13,37</t>
+          <t>7,64; 13,23</t>
         </is>
       </c>
     </row>
@@ -1069,54 +1069,54 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,06%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>10,67%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>6,45%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,94</t>
+          <t>5,87; 12,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,86</t>
+          <t>9,65; 18,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,49</t>
+          <t>3,93; 10,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 17,72</t>
+          <t>9,26; 22,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 12,35</t>
+          <t>2,3; 7,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 18,12</t>
+          <t>4,95; 11,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,13</t>
+          <t>3,54; 9,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 25,92</t>
+          <t>6,83; 13,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,65</t>
+          <t>4,6; 8,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 13,43</t>
+          <t>7,97; 13,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,25</t>
+          <t>4,42; 8,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 18,43</t>
+          <t>9,19; 17,3</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,07</t>
+          <t>9,79; 13,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,68</t>
+          <t>11,36; 15,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,48</t>
+          <t>5,57; 8,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,47</t>
+          <t>10,22; 16,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,63; 13,65</t>
+          <t>6,7; 10,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 15,44</t>
+          <t>9,9; 13,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,43</t>
+          <t>5,26; 8,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,59; 17,58</t>
+          <t>7,63; 11,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 11,39</t>
+          <t>8,77; 11,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 14,05</t>
+          <t>11,32; 14,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,02</t>
+          <t>5,86; 8,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,09</t>
+          <t>9,47; 13,49</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15530</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24939</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>10005</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>21008</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>9682</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15530</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24939</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>17189</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6113; 15984</t>
+          <t>10526; 22107</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14983; 29238</t>
+          <t>17996; 32637</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5853; 14962</t>
+          <t>7988; 18882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4673; 12423</t>
+          <t>6036; 13681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10712; 22454</t>
+          <t>5653; 15290</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18507; 33630</t>
+          <t>14791; 28564</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8153; 18783</t>
+          <t>5624; 15880</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6807; 16677</t>
+          <t>4335; 12558</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18853; 34273</t>
+          <t>18555; 35136</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37249; 56912</t>
+          <t>37243; 56444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15676; 30372</t>
+          <t>15949; 30342</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14362; 26313</t>
+          <t>11807; 23206</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>24665</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>28288</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18516</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38421</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17972; 32826</t>
+          <t>26592; 44085</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20191; 36197</t>
+          <t>29641; 48268</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12574; 25096</t>
+          <t>14395; 28589</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5822; 15270</t>
+          <t>13343; 26187</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26562; 44309</t>
+          <t>18009; 33173</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30614; 50071</t>
+          <t>20966; 36989</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14773; 29069</t>
+          <t>12937; 25993</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15205; 30644</t>
+          <t>5526; 14105</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48698; 71909</t>
+          <t>48212; 71762</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55199; 80129</t>
+          <t>55037; 79674</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30762; 50274</t>
+          <t>30730; 49904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24001; 40925</t>
+          <t>21182; 36459</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>13699</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>20199</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8903</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9090; 21371</t>
+          <t>9602; 22043</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13639; 27423</t>
+          <t>9907; 22185</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4935; 15427</t>
+          <t>2751; 10915</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10770; 24872</t>
+          <t>14362; 31340</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9683; 22717</t>
+          <t>8593; 20494</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9583; 22429</t>
+          <t>13677; 28206</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2293; 10563</t>
+          <t>4894; 14728</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15497; 34091</t>
+          <t>11231; 25637</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21680; 38122</t>
+          <t>20669; 37964</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26147; 44501</t>
+          <t>26740; 44256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9336; 22000</t>
+          <t>9574; 23493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29662; 51539</t>
+          <t>28645; 49588</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24098</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7874</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13375</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24098</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4226; 13475</t>
+          <t>12087; 25179</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8482; 20317</t>
+          <t>17365; 32422</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5949; 18095</t>
+          <t>6834; 18863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18549; 48746</t>
+          <t>26896; 65940</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11897; 25453</t>
+          <t>4460; 13868</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17297; 32616</t>
+          <t>8488; 19858</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6624; 17635</t>
+          <t>6108; 16759</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27264; 78653</t>
+          <t>17500; 34254</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18420; 34620</t>
+          <t>18421; 34425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28823; 47173</t>
+          <t>27996; 48032</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15680; 32061</t>
+          <t>15314; 31030</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51887; 106618</t>
+          <t>50216; 94571</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>47647</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45465; 68573</t>
+          <t>70691; 97757</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69593; 97242</t>
+          <t>85622; 117859</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37234; 59554</t>
+          <t>41347; 63119</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49148; 82883</t>
+          <t>71419; 114800</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>69555; 98523</t>
+          <t>45625; 69264</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87486; 116351</t>
+          <t>70360; 96227</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40454; 62554</t>
+          <t>36956; 59632</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80504; 133640</t>
+          <t>47941; 71961</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>120983; 159801</t>
+          <t>122977; 158856</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164447; 205744</t>
+          <t>165806; 207696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83244; 115865</t>
+          <t>84660; 116464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>137584; 200782</t>
+          <t>125646; 178982</t>
         </is>
       </c>
     </row>
